--- a/tests/data/test_data.xlsx
+++ b/tests/data/test_data.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\32723\Desktop\kuki\PythonProject1\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A40EE4D-9D88-468F-B499-9B9EEDBAA281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBEB6C2-B551-4886-AC22-2C1080DB2A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1808" yWindow="2865" windowWidth="16199" windowHeight="9308" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="2" r:id="rId1"/>
     <sheet name="Login" sheetId="1" r:id="rId2"/>
+    <sheet name="Checkout" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
   <si>
     <t>Filter</t>
   </si>
@@ -87,8 +88,142 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>1python</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <t>from_email</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>758844606@qq.com</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>to_email</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>password</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>hpdxdltallxhbfei</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>发送人</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>收件人</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>邮箱授权码</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>smtp_server</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>smtp_port</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>smtp.qq.com</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>项目名</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>URL</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>服务器</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>服务器端口号</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>remark</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>fisrt2_user</t>
+  </si>
+  <si>
+    <t>fisrt3_user</t>
+  </si>
+  <si>
+    <t>fisrt4_user</t>
+  </si>
+  <si>
+    <t>fisrt5_user</t>
+  </si>
+  <si>
+    <t>fisrt6_user</t>
+  </si>
+  <si>
+    <t>last3</t>
+  </si>
+  <si>
+    <t>last4</t>
+  </si>
+  <si>
+    <t>last5</t>
+  </si>
+  <si>
+    <t>last6</t>
+  </si>
+  <si>
+    <t>code 2</t>
+  </si>
+  <si>
+    <t>code 4</t>
+  </si>
+  <si>
+    <t>code 5</t>
+  </si>
+  <si>
+    <t>code 6</t>
+  </si>
+  <si>
+    <t>missCol</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>First Name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Last Name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Postal Code</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>user1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>user2</t>
+  </si>
+  <si>
+    <t>user3</t>
+  </si>
+  <si>
+    <t>user4</t>
+  </si>
+  <si>
+    <t>user5</t>
+  </si>
+  <si>
+    <t>user6</t>
   </si>
 </sst>
 </file>
@@ -156,10 +291,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -463,45 +606,111 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0F8313D-5E13-4E03-AB44-C4C6C8F8FAC0}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.9296875" customWidth="1"/>
+    <col min="2" max="2" width="28.3984375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18.53125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>12</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="C3" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2">
+        <v>465</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G8" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G10" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{63ECBBA4-9DF5-475D-A76F-A6D64B857B70}"/>
+    <hyperlink ref="B6" r:id="rId2" xr:uid="{6522DD32-48E1-4A04-A0E1-19DB6C17EA38}"/>
+    <hyperlink ref="B7" r:id="rId3" xr:uid="{0FAB37A9-1F6D-48C4-AAB7-C7B65B988046}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -564,4 +773,122 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC5902CF-1D4D-4A3A-A626-F1E58D435FEF}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="12.265625" customWidth="1"/>
+    <col min="3" max="5" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/tests/data/test_data.xlsx
+++ b/tests/data/test_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\32723\Desktop\kuki\PythonProject1\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EBEB6C2-B551-4886-AC22-2C1080DB2A55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{316A103D-AC20-41DC-B1D5-F19F0689E639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="58">
   <si>
     <t>Filter</t>
   </si>
@@ -224,6 +224,18 @@
   </si>
   <si>
     <t>user6</t>
+  </si>
+  <si>
+    <t>tester</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>关曼清</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试人员名字</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -702,6 +714,17 @@
         <v>23</v>
       </c>
     </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="G10" s="1"/>
     </row>
